--- a/FinanceDataMigration/src/main/resources/migration-templates/SUPPLIER_BILL.xlsx
+++ b/FinanceDataMigration/src/main/resources/migration-templates/SUPPLIER_BILL.xlsx
@@ -418,7 +418,7 @@
     <font>
       <b/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font/>
@@ -477,14 +477,14 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="none"/>
@@ -492,11 +492,11 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -505,7 +505,7 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -513,46 +513,46 @@
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -560,38 +560,38 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -1844,19 +1844,8 @@
     <mergeCell ref="T6:W6"/>
     <mergeCell ref="X6:Y6"/>
   </mergeCells>
-  <dataValidations count="4" disablePrompts="0">
-    <dataValidation sqref="H8:H22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$B$2:$B$40</formula1>
-    </dataValidation>
-    <dataValidation sqref="L8:L22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="C8:C22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="P8:P22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$H$2:$H$5</formula1>
-    </dataValidation>
+  <dataValidations count="1" disablePrompts="0">
+    <dataValidation sqref="1:1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
